--- a/batchtest/Results/StudentsSolution.xlsx
+++ b/batchtest/Results/StudentsSolution.xlsx
@@ -43,7 +43,7 @@
     <x:t>FAILED</x:t>
   </x:si>
   <x:si>
-    <x:t>Error: [SharedNetworkMonitor] CRITICAL: No suitable capture device found! On Linux, ensure libpcap is installed and run with sudo. On Windows, ensure NPcap is installed.</x:t>
+    <x:t/>
   </x:si>
   <x:si>
     <x:t>anlpvhe187047</x:t>
@@ -429,7 +429,7 @@
     <x:col min="3" max="3" width="6.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="10.139196" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="155.282054" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="5.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6" s="1" customFormat="1">
